--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45988.375</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -668,61 +668,61 @@
         <v>4.68</v>
       </c>
       <c r="O2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
         <v>2.74</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
         <v>3.34</v>
       </c>
       <c r="AA2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.92</v>
       </c>
       <c r="AC2" t="n">
         <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
         <v>2.05</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -662,37 +662,37 @@
         <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
         <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -701,10 +701,10 @@
         <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
@@ -713,7 +713,7 @@
         <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
         <v>1.78</v>
@@ -906,40 +906,40 @@
         <v>1.94</v>
       </c>
       <c r="O4" t="n">
-        <v>4.01</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.05</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA4" t="n">
         <v>1.85</v>
@@ -951,7 +951,7 @@
         <v>3.08</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
         <v>1.73</v>
@@ -963,7 +963,7 @@
         <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45988.375</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2215,40 +2215,40 @@
         <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
         <v>1.8</v>
@@ -2257,22 +2257,22 @@
         <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -662,37 +662,37 @@
         <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
         <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>5.47</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -704,16 +704,16 @@
         <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
         <v>1.78</v>
@@ -722,10 +722,10 @@
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
         <v>3.75</v>
@@ -918,28 +918,28 @@
         <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="T4" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
         <v>1.85</v>
@@ -954,7 +954,7 @@
         <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AF4" t="n">
         <v>2</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -665,16 +665,16 @@
         <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="P2" t="n">
         <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.47</v>
+        <v>5.18</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -683,7 +683,7 @@
         <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
@@ -701,16 +701,16 @@
         <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
         <v>1.3</v>
@@ -722,10 +722,10 @@
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -915,7 +915,7 @@
         <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
         <v>2.83</v>
@@ -936,7 +936,7 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
         <v>3.34</v>
@@ -951,7 +951,7 @@
         <v>3.08</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
         <v>1.69</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>45988.45833333334</v>
+        <v>45988.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2221,22 +2221,22 @@
         <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.01</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
         <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
@@ -2245,10 +2245,10 @@
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="AA15" t="n">
         <v>1.8</v>
@@ -2260,13 +2260,13 @@
         <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
         <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG15" t="n">
         <v>1.29</v>
@@ -2334,19 +2334,19 @@
         <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.33</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
         <v>3.48</v>
@@ -2355,19 +2355,19 @@
         <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AA16" t="n">
         <v>2.45</v>
@@ -2376,7 +2376,7 @@
         <v>1.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AD16" t="n">
         <v>1.17</v>
@@ -2391,7 +2391,7 @@
         <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -668,22 +668,22 @@
         <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.18</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
         <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
@@ -701,16 +701,16 @@
         <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AD2" t="n">
         <v>1.3</v>
@@ -722,10 +722,10 @@
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P4" t="n">
         <v>2.2</v>
@@ -918,13 +918,13 @@
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
         <v>6.65</v>
@@ -933,10 +933,10 @@
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
         <v>3.34</v>
@@ -948,7 +948,7 @@
         <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD4" t="n">
         <v>1.3</v>
@@ -960,10 +960,10 @@
         <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45988.375</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="O15" t="n">
         <v>2.27</v>
@@ -2221,13 +2221,13 @@
         <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>3.07</v>
       </c>
       <c r="T15" t="n">
         <v>2.66</v>
@@ -2236,7 +2236,7 @@
         <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
@@ -2245,34 +2245,34 @@
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
         <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
         <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="P16" t="n">
         <v>1.89</v>
@@ -2346,7 +2346,7 @@
         <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="T16" t="n">
         <v>3.48</v>
@@ -2361,37 +2361,37 @@
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AA16" t="n">
         <v>2.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AC16" t="n">
         <v>4.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2325,31 +2325,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
         <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
         <v>1.26</v>
@@ -2370,28 +2370,28 @@
         <v>2.51</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -665,22 +665,22 @@
         <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
         <v>2.67</v>
@@ -689,7 +689,7 @@
         <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
@@ -698,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
         <v>3.6</v>
@@ -707,7 +707,7 @@
         <v>1.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC2" t="n">
         <v>3.15</v>
@@ -716,13 +716,13 @@
         <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
@@ -903,16 +903,16 @@
         <v>3.59</v>
       </c>
       <c r="N4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65</v>
+        <v>4.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -924,34 +924,34 @@
         <v>2.71</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.05</v>
       </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
         <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
         <v>1.69</v>
@@ -960,7 +960,7 @@
         <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AH4" t="n">
         <v>1.12</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,40 +2206,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.68</v>
+        <v>3.53</v>
       </c>
       <c r="N15" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
@@ -2251,28 +2251,28 @@
         <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.87</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="P16" t="n">
         <v>1.9</v>
@@ -2346,37 +2346,37 @@
         <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
         <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z16" t="n">
         <v>2.51</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
         <v>1.18</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2221,16 +2221,16 @@
         <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>3.07</v>
       </c>
       <c r="T15" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
         <v>1.4</v>
@@ -2239,10 +2239,10 @@
         <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>1.28</v>
@@ -2260,16 +2260,16 @@
         <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
         <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
         <v>1.91</v>
@@ -2340,28 +2340,28 @@
         <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="T16" t="n">
         <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.48</v>
@@ -2379,7 +2379,7 @@
         <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
         <v>2.1</v>
@@ -2388,10 +2388,10 @@
         <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -665,22 +665,22 @@
         <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>5.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
         <v>2.67</v>
@@ -698,34 +698,34 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
         <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
         <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="M4" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O4" t="n">
-        <v>4.18</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="T4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
         <v>1.37</v>
@@ -930,7 +930,7 @@
         <v>7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>
@@ -939,19 +939,19 @@
         <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
         <v>1.69</v>
@@ -960,10 +960,10 @@
         <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45988.375</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="M15" t="n">
-        <v>3.53</v>
+        <v>3.69</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
         <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="T15" t="n">
         <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
         <v>6.5</v>
@@ -2242,7 +2242,7 @@
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
         <v>1.28</v>
@@ -2251,13 +2251,13 @@
         <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD15" t="n">
         <v>1.33</v>
@@ -2266,13 +2266,13 @@
         <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
         <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="P16" t="n">
         <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
         <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
         <v>5</v>
@@ -2385,7 +2385,7 @@
         <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
         <v>1.33</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="O16" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="P16" t="n">
         <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AB16" t="n">
         <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE16" t="n">
         <v>2.1</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.69</v>
+        <v>3.53</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
@@ -2248,31 +2248,31 @@
         <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -659,31 +659,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.41</v>
+        <v>5.18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
@@ -692,40 +692,40 @@
         <v>6.5</v>
       </c>
       <c r="W2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1.05</v>
       </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.86</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -784,7 +784,7 @@
         <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="O3" t="n">
         <v>2.5</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="N4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
         <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="R4" t="n">
         <v>1.34</v>
@@ -921,10 +921,10 @@
         <v>2.83</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
         <v>7</v>
@@ -936,31 +936,31 @@
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
         <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
         <v>1.3</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="R16" t="n">
         <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC16" t="n">
         <v>4.75</v>
@@ -2385,13 +2385,13 @@
         <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="M2" t="n">
         <v>3.75</v>
@@ -668,34 +668,34 @@
         <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.18</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
         <v>1.26</v>
@@ -704,28 +704,28 @@
         <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="P3" t="n">
         <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB3" t="n">
         <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45988.29166666666</v>
@@ -909,10 +909,10 @@
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
         <v>1.34</v>
@@ -927,7 +927,7 @@
         <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
@@ -936,10 +936,10 @@
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AA4" t="n">
         <v>1.86</v>
@@ -948,22 +948,22 @@
         <v>1.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45988.375</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.9</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.24</v>
       </c>
       <c r="O3" t="n">
         <v>2.52</v>
@@ -823,10 +823,10 @@
         <v>2.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC3" t="n">
         <v>5.5</v>
@@ -1019,10 +1019,10 @@
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
@@ -1061,10 +1061,10 @@
         <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
         <v>6.5</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
@@ -1180,10 +1180,10 @@
         <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC6" t="n">
         <v>5.5</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2218,10 +2218,10 @@
         <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
@@ -2248,7 +2248,7 @@
         <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.8</v>
@@ -2260,19 +2260,19 @@
         <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2337,16 +2337,16 @@
         <v>2.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
         <v>4.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
         <v>3.4</v>
@@ -2361,13 +2361,13 @@
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA16" t="n">
         <v>2.45</v>
@@ -2376,7 +2376,7 @@
         <v>1.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AD16" t="n">
         <v>1.16</v>
@@ -2388,10 +2388,10 @@
         <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.24</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
         <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.21</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
         <v>9.5</v>
@@ -814,37 +814,37 @@
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45988.29166666666</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.51</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
         <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.7</v>
+        <v>4.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
         <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>3.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3.05</v>
       </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
         <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>2.8</v>
@@ -823,10 +823,10 @@
         <v>2.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC3" t="n">
         <v>4.45</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
         <v>3.42</v>
@@ -1055,16 +1055,16 @@
         <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.07</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
         <v>5.8</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
         <v>3.9</v>
@@ -1180,10 +1180,10 @@
         <v>2.31</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC6" t="n">
         <v>5.1</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="M2" t="n">
         <v>3.75</v>
@@ -668,28 +668,28 @@
         <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -698,34 +698,34 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="M4" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
         <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="T4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
         <v>6.65</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45988.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.32</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.9</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.15</v>
+        <v>5.01</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
         <v>6.6</v>
@@ -2242,37 +2242,37 @@
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
         <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2325,28 +2325,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="O16" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
         <v>3.4</v>
@@ -2355,7 +2355,7 @@
         <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
@@ -2367,31 +2367,31 @@
         <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AC16" t="n">
         <v>4.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.9</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>13</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.32</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.32</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.9</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>4.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
         <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
         <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45988.29166666666</v>
@@ -1019,10 +1019,10 @@
         <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O5" t="n">
         <v>3.9</v>
@@ -1034,16 +1034,16 @@
         <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
         <v>2.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
         <v>11</v>
@@ -1055,10 +1055,10 @@
         <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
         <v>2.65</v>
@@ -1067,22 +1067,22 @@
         <v>1.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
         <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
         <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
         <v>2.73</v>
@@ -1186,22 +1186,22 @@
         <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.01</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
@@ -2248,31 +2248,31 @@
         <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
         <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -659,40 +659,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.3</v>
+        <v>5.67</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
         <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V2" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -701,16 +701,16 @@
         <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
         <v>1.33</v>
@@ -719,13 +719,13 @@
         <v>1.79</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45988.22916666666</v>
@@ -897,43 +897,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>4.46</v>
+        <v>4.57</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.28</v>
@@ -951,19 +951,19 @@
         <v>3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45988.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.1</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.9</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.58</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>9.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA6" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -781,34 +781,34 @@
         <v>2.15</v>
       </c>
       <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O3" t="n">
         <v>2.85</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.87</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
         <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -820,10 +820,10 @@
         <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="AB3" t="n">
         <v>1.5</v>
@@ -838,10 +838,10 @@
         <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
         <v>1.54</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="R5" t="n">
         <v>1.66</v>
@@ -1040,7 +1040,7 @@
         <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="U5" t="n">
         <v>1.16</v>
@@ -1055,31 +1055,31 @@
         <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
         <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
         <v>6.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
         <v>2.31</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
         <v>1.44</v>
@@ -1138,52 +1138,52 @@
         <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
         <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
         <v>2.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
         <v>5.2</v>
@@ -1198,7 +1198,7 @@
         <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
         <v>1.27</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -764,17 +764,17 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O4" t="n">
-        <v>4.57</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
         <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD4" t="n">
         <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45988.375</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AE5" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA6" t="n">
         <v>3.1</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AB6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA5" t="n">
         <v>3.1</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AB5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AE6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2215,40 +2215,40 @@
         <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="U15" t="n">
         <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA15" t="n">
         <v>1.8</v>
@@ -2257,22 +2257,22 @@
         <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2337,37 +2337,37 @@
         <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.2</v>
+        <v>5.22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
         <v>2.45</v>
@@ -2376,22 +2376,22 @@
         <v>1.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE16" t="n">
         <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,22 +990,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AE5" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA6" t="n">
         <v>3.1</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AB6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,22 +990,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA5" t="n">
         <v>3.1</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AB5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AE6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.66</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AF15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.03</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45988.70833333334</v>
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.01</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T16" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
         <v>9.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
         <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
         <v>2.2</v>
@@ -2388,10 +2388,10 @@
         <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45988.85416666666</v>

--- a/jogos_2025-11-27.xlsx
+++ b/jogos_2025-11-27.xlsx
@@ -990,22 +990,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AE5" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA6" t="n">
         <v>3.1</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AB6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45988.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2189,20 +2189,20 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
